--- a/dcf/HEI.xlsx
+++ b/dcf/HEI.xlsx
@@ -863,7 +863,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1119,25 +1119,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.06846881111633073</v>
+        <v>0.06843134561886265</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.07346881111633073</v>
+        <v>0.07343134561886265</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.07846881111633072</v>
+        <v>0.07843134561886264</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.08346881111633073</v>
+        <v>0.08343134561886265</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.08846881111633073</v>
+        <v>0.08843134561886265</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.09346881111633072</v>
+        <v>0.09343134561886264</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.09846881111633073</v>
+        <v>0.09843134561886265</v>
       </c>
     </row>
     <row r="5">
@@ -1145,25 +1145,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>125.1252452619956</v>
+        <v>125.1650003238305</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>119.943748122494</v>
+        <v>119.9816740241157</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>114.9999116176758</v>
+        <v>115.0361034057613</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>110.2814192632411</v>
+        <v>110.3159665665964</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>105.7766549094625</v>
+        <v>105.8096422730909</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>101.4746596608733</v>
+        <v>101.5061668579525</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>97.36509163764926</v>
+        <v>97.39519396098122</v>
       </c>
     </row>
     <row r="6">
@@ -1171,25 +1171,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>134.0385146890339</v>
+        <v>134.0813957614826</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>128.4504501620826</v>
+        <v>128.4913455865006</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>123.1203528851154</v>
+        <v>123.1593662152459</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>118.0348049436766</v>
+        <v>118.0720338166555</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>113.1811531856844</v>
+        <v>113.2166896874551</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>108.5474621007779</v>
+        <v>108.5813931073131</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>104.1224698116157</v>
+        <v>104.1548773076601</v>
       </c>
     </row>
     <row r="7">
@@ -1197,25 +1197,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>142.9517841160722</v>
+        <v>142.9977911991348</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>136.9571522016711</v>
+        <v>137.0010171488856</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>131.240794152555</v>
+        <v>131.2826290247305</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>125.7881906241121</v>
+        <v>125.8281010667146</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>120.5856514619063</v>
+        <v>120.6237371018192</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>115.6202645406826</v>
+        <v>115.6566193566736</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>110.8798479855822</v>
+        <v>110.914560654339</v>
       </c>
     </row>
     <row r="8">
@@ -1223,25 +1223,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>151.8650535431104</v>
+        <v>151.9141866367868</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>145.4638542412597</v>
+        <v>145.5106887112705</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>139.3612354199946</v>
+        <v>139.4058918342151</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>133.5415763045476</v>
+        <v>133.5841683167737</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>127.9901497381282</v>
+        <v>128.0307845161834</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>122.6930669805872</v>
+        <v>122.7318456060341</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>117.6372261595486</v>
+        <v>117.6742440010178</v>
       </c>
     </row>
     <row r="9">
@@ -1249,25 +1249,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>160.7783229701487</v>
+        <v>160.830582074439</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>153.9705562808483</v>
+        <v>154.0203602736554</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>147.4816766874342</v>
+        <v>147.5291546436996</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>141.2949619849832</v>
+        <v>141.3402355668328</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>135.3946480143501</v>
+        <v>135.4378319305476</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>129.7658694204918</v>
+        <v>129.8070718553946</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>124.3946043335151</v>
+        <v>124.4339273476967</v>
       </c>
     </row>
     <row r="10">
@@ -1275,25 +1275,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>169.691592397187</v>
+        <v>169.7469775120911</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>162.4772583204368</v>
+        <v>162.5300318360403</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>155.6021179548738</v>
+        <v>155.6524174531843</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>149.0483476654187</v>
+        <v>149.0963028168919</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>142.799146290572</v>
+        <v>142.8448793449118</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>136.8386718603965</v>
+        <v>136.8822981047552</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>131.1519825074816</v>
+        <v>131.1936106943756</v>
       </c>
     </row>
     <row r="11">
@@ -1301,25 +1301,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>178.6048618242252</v>
+        <v>178.6633729497432</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>170.9839603600254</v>
+        <v>171.0397033984252</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>163.7225592223134</v>
+        <v>163.7756802626688</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>156.8017333458542</v>
+        <v>156.852370066951</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>150.2036445667939</v>
+        <v>150.251926759276</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>143.9114743003011</v>
+        <v>143.9575243541157</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>137.909360681448</v>
+        <v>137.9532940410544</v>
       </c>
     </row>
     <row r="13">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>362.0899963378906</v>
+        <v>356.2900085449219</v>
       </c>
     </row>
     <row r="14">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.08346881111633073</v>
+        <v>0.08343134561886265</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.9994769685775764</v>
+        <v>0.9994767805435035</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24456,7 +24456,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>362.0899963378906</v>
+        <v>356.2900085449219</v>
       </c>
     </row>
     <row r="49">
@@ -24618,13 +24618,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>133.5415763045476</v>
+        <v>133.5841683167737</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>192.327500854564</v>
+        <v>192.388927033271</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>90.08946549410568</v>
+        <v>90.11834333218671</v>
       </c>
     </row>
     <row r="59">
